--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -748,394 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45910.45833333334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Zrinjski</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="3" t="n">
         <v>45910.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Chicago Fire II</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>FC Cincinnati II</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="3" t="n">
-        <v>45910.66666666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Detroit City FC</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="3" t="n">
-        <v>45910.91666666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,127 +628,514 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Buxoro</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>45910.45833333334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Zrinjski</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Sarajevo</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="L3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45910.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chicago Fire II</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>45910.66666666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>45910.91666666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.5</v>
+        <v>45910.625</v>
       </c>
     </row>
     <row r="4">

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.625</v>
+        <v>45910.5</v>
       </c>
     </row>
     <row r="4">

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -807,34 +807,34 @@
         <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y3" t="n">
         <v>2.12</v>
@@ -843,16 +843,16 @@
         <v>1.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -801,46 +801,46 @@
         <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="O3" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.66</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
         <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
@@ -849,10 +849,10 @@
         <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="M3" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
         <v>2.25</v>
@@ -837,10 +837,10 @@
         <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.5</v>
+        <v>45910.625</v>
       </c>
     </row>
     <row r="4">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.66</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
@@ -831,22 +831,22 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
         <v>2.1</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -1065,34 +1065,34 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y5" t="n">
         <v>2</v>
@@ -1101,16 +1101,16 @@
         <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
         <v>5.66</v>
@@ -822,10 +822,10 @@
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
@@ -834,13 +834,13 @@
         <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
@@ -852,7 +852,7 @@
         <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
@@ -1074,10 +1074,10 @@
         <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
         <v>2.88</v>
@@ -1086,31 +1086,31 @@
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="Y5" t="n">
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
         <v>1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -1080,16 +1080,16 @@
         <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
         <v>3.05</v>
@@ -1101,16 +1101,16 @@
         <v>1.73</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.25</v>
@@ -825,7 +825,7 @@
         <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
@@ -834,25 +834,25 @@
         <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
         <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.625</v>
+        <v>45910.5</v>
       </c>
     </row>
     <row r="4">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
@@ -1071,13 +1071,13 @@
         <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
         <v>2.89</v>
@@ -1086,10 +1086,10 @@
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
         <v>3.05</v>
@@ -1098,19 +1098,19 @@
         <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.5</v>
+        <v>45910.625</v>
       </c>
     </row>
     <row r="4">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -1068,19 +1068,19 @@
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
@@ -1092,7 +1092,7 @@
         <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Y5" t="n">
         <v>2</v>
@@ -1104,10 +1104,10 @@
         <v>3.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
         <v>1.91</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>4.57</v>
       </c>
       <c r="O3" t="n">
         <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
         <v>5.66</v>
@@ -831,7 +831,7 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
         <v>2.78</v>
@@ -840,16 +840,16 @@
         <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
         <v>1.67</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1056,31 +1056,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
@@ -1095,22 +1095,22 @@
         <v>3.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AA5" t="n">
         <v>3.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>4.57</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.66</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
         <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
         <v>1.36</v>
@@ -840,7 +840,7 @@
         <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
@@ -849,7 +849,7 @@
         <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
         <v>1.67</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
         <v>3.55</v>
@@ -1077,7 +1077,7 @@
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
         <v>2.8</v>
@@ -1086,28 +1086,28 @@
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
         <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AA5" t="n">
         <v>3.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD5" t="n">
         <v>1.93</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -807,34 +807,34 @@
         <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="P3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
         <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
         <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
         <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Y3" t="n">
         <v>2.1</v>
@@ -849,10 +849,10 @@
         <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
         <v>2.05</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.625</v>
+        <v>45910.5</v>
       </c>
     </row>
     <row r="4">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
         <v>2.8</v>
@@ -1095,22 +1095,22 @@
         <v>3.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
         <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
         <v>1.62</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>4.69</v>
       </c>
       <c r="O3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
         <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
         <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45910.5</v>
+        <v>45910.625</v>
       </c>
     </row>
     <row r="4">

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>4.69</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.3</v>
@@ -837,7 +837,7 @@
         <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
         <v>1.65</v>
@@ -1065,22 +1065,22 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
@@ -1092,7 +1092,7 @@
         <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
         <v>2</v>
@@ -1101,16 +1101,16 @@
         <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB5" t="n">
         <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N2" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45910.45833333334</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="P3" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="T3" t="n">
         <v>3.14</v>
@@ -834,25 +834,25 @@
         <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45910.625</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45910.66666666666</v>
@@ -1056,49 +1056,49 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
         <v>3.55</v>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45910.91666666666</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.88</v>
@@ -687,31 +687,31 @@
         <v>7.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
         <v>3.4</v>
@@ -720,10 +720,10 @@
         <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.33</v>
@@ -813,16 +813,16 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.49</v>
       </c>
       <c r="T3" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
         <v>1.33</v>
@@ -831,16 +831,16 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
         <v>2.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
         <v>3.8</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="n">
         <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
         <v>2.37</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="N5" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
@@ -1095,10 +1095,10 @@
         <v>3.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
         <v>3.55</v>
@@ -1107,10 +1107,10 @@
         <v>1.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI5" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-10.xlsx
+++ b/jogos_2025-09-10.xlsx
@@ -678,13 +678,13 @@
         <v>9.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -693,7 +693,7 @@
         <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
@@ -705,7 +705,7 @@
         <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Y2" t="n">
         <v>1.8</v>
@@ -714,16 +714,16 @@
         <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AB2" t="n">
         <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
@@ -807,34 +807,34 @@
         <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
         <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Y3" t="n">
         <v>2.1</v>
@@ -843,13 +843,13 @@
         <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD3" t="n">
         <v>1.64</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AI3" t="n">
         <v>1.61</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="O4" t="n">
         <v>2.37</v>
@@ -1068,10 +1068,10 @@
         <v>2.84</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
@@ -1089,10 +1089,10 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
         <v>2</v>
@@ -1104,10 +1104,10 @@
         <v>3.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD5" t="n">
         <v>2</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>1.83</v>
